--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Gray_2024_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Gray_2024_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{D6FDD79B-056F-1B49-B921-33F727076B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A10E616-15C1-4160-B161-F1384B01E0DE}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -804,7 +804,7 @@
         </row>
         <row r="19">
           <cell r="C19">
-            <v>0.8</v>
+            <v>1.7</v>
           </cell>
         </row>
         <row r="21">
@@ -849,12 +849,12 @@
         </row>
         <row r="33">
           <cell r="C33">
-            <v>1282</v>
+            <v>1371</v>
           </cell>
         </row>
         <row r="34">
           <cell r="C34">
-            <v>480</v>
+            <v>523</v>
           </cell>
         </row>
       </sheetData>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C18" s="5">
         <f>[1]Inputs!C19</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C32" s="5">
         <f>[1]Inputs!C33</f>
-        <v>1282</v>
+        <v>1371</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C33" s="5">
         <f>[1]Inputs!C34</f>
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="B7" s="17">
         <f>Inputs!C33 * Inputs!C6</f>
-        <v>432</v>
+        <v>470.7</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>74</v>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="F7" s="17">
         <f>Inputs!C32*Inputs!C6</f>
-        <v>1153.8</v>
+        <v>1233.9000000000001</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>74</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="B8" s="13">
         <f>B7*B6*10^3 / 10^6</f>
-        <v>62.356608000000001</v>
+        <v>67.942720800000004</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>80</v>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="F8" s="13">
         <f>F7*F6*10^3 / 10^6</f>
-        <v>166.54410719999998</v>
+        <v>178.10606160000003</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>80</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B14" s="13">
         <f>(B4+B8+B11)  * 10^6/ B12</f>
-        <v>479.49076767585217</v>
+        <v>494.49509966618257</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>71</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="F14" s="13">
         <f>(F4+F8+F11)  * 10^6/ F12</f>
-        <v>759.33900619317683</v>
+        <v>790.39448403362826</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>71</v>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="B15" s="13">
         <f>B14*'Study Parameters'!$C$28/10^3</f>
-        <v>5.7011452276658829</v>
+        <v>5.8795467350309112</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>120</v>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="F15" s="13">
         <f>F14*'Study Parameters'!$C$28/10^3</f>
-        <v>9.0285407836368723</v>
+        <v>9.3977904151598413</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>120</v>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="B16" s="10">
         <f>B15 * Inputs!$C$15</f>
-        <v>4.5780196178157047</v>
+        <v>4.7212760282298216</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>121</v>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="F16" s="10">
         <f>F15 * Inputs!$C$15</f>
-        <v>7.2499182492604088</v>
+        <v>7.5464257033733526</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>121</v>
@@ -3915,14 +3915,14 @@
       </c>
       <c r="J2" s="5">
         <f>F8</f>
-        <v>166.54410719999998</v>
+        <v>178.10606160000003</v>
       </c>
       <c r="L2" t="s">
         <v>94</v>
       </c>
       <c r="M2" s="5">
         <f>B8</f>
-        <v>62.356608000000001</v>
+        <v>67.942720800000004</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="B7" s="17">
         <f>Inputs!C33 * Inputs!C6</f>
-        <v>432</v>
+        <v>470.7</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>74</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="F7" s="17">
         <f>Inputs!C32*Inputs!C6</f>
-        <v>1153.8</v>
+        <v>1233.9000000000001</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>74</v>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="B8" s="13">
         <f>B7*B6*10^3 / 10^6</f>
-        <v>62.356608000000001</v>
+        <v>67.942720800000004</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>80</v>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="F8" s="13">
         <f>F7*F6*10^3 / 10^6</f>
-        <v>166.54410719999998</v>
+        <v>178.10606160000003</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>80</v>
@@ -4109,14 +4109,14 @@
       </c>
       <c r="J8" s="20">
         <f>J2/SUM($J$2:$J$5)</f>
-        <v>0.62092679072229295</v>
+        <v>0.6365920229031099</v>
       </c>
       <c r="L8" t="s">
         <v>94</v>
       </c>
       <c r="M8" s="20">
         <f>M2/SUM($M$2:$M$5)</f>
-        <v>0.38015115530719518</v>
+        <v>0.40056503743767941</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4145,14 +4145,14 @@
       </c>
       <c r="J9" s="20">
         <f t="shared" ref="J9:J11" si="0">J3/SUM($J$2:$J$5)</f>
-        <v>0.21490233164290276</v>
+        <v>0.20602147475565522</v>
       </c>
       <c r="L9" t="s">
         <v>93</v>
       </c>
       <c r="M9" s="20">
         <f t="shared" ref="M9:M11" si="1">M3/SUM($M$2:$M$5)</f>
-        <v>0.35140167843688636</v>
+        <v>0.33982874012219116</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4181,14 +4181,14 @@
       </c>
       <c r="J10" s="20">
         <f t="shared" si="0"/>
-        <v>0.11197464435905774</v>
+        <v>0.10734728278530967</v>
       </c>
       <c r="L10" t="s">
         <v>86</v>
       </c>
       <c r="M10" s="20">
         <f t="shared" si="1"/>
-        <v>0.18309749209948045</v>
+        <v>0.17706742419807384</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4217,14 +4217,14 @@
       </c>
       <c r="J11" s="20">
         <f t="shared" si="0"/>
-        <v>5.2196233275746323E-2</v>
+        <v>5.0039219555925198E-2</v>
       </c>
       <c r="L11" t="s">
         <v>123</v>
       </c>
       <c r="M11" s="20">
         <f t="shared" si="1"/>
-        <v>8.534967415643796E-2</v>
+        <v>8.2538798242055553E-2</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="B14" s="13">
         <f>(B4+B8+B11)  * 10^6/ B12</f>
-        <v>500.05249684948058</v>
+        <v>515.05682883981103</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>71</v>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="F14" s="13">
         <f>(F4+F8+F11)  * 10^6/ F12</f>
-        <v>779.90073536680541</v>
+        <v>810.95621320725672</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>71</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="B15" s="13">
         <f>B14*'Study Parameters'!$C$28/10^3</f>
-        <v>5.9456241875403251</v>
+        <v>6.1240256949053533</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>120</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="F15" s="13">
         <f>F14*'Study Parameters'!$C$28/10^3</f>
-        <v>9.2730197435113162</v>
+        <v>9.6422693750342816</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>120</v>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="B16" s="10">
         <f>B15 * Inputs!$C$15</f>
-        <v>4.7743362225948811</v>
+        <v>4.917592633008999</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>121</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F16" s="10">
         <f>F15 * Inputs!$C$15</f>
-        <v>7.4462348540395871</v>
+        <v>7.7427423081525282</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>121</v>
@@ -4416,11 +4416,11 @@
       </c>
       <c r="E3" s="10">
         <f>'LCOF DAC Corrected'!B16</f>
-        <v>4.5780196178157047</v>
+        <v>4.7212760282298216</v>
       </c>
       <c r="F3" s="10">
         <f>'LCOF WACC Corrected'!B16</f>
-        <v>4.7743362225948811</v>
+        <v>4.917592633008999</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>131</v>
@@ -4438,11 +4438,11 @@
       </c>
       <c r="L3" s="10">
         <f>'LCOF DAC Corrected'!F16</f>
-        <v>7.2499182492604088</v>
+        <v>7.5464257033733526</v>
       </c>
       <c r="M3" s="10">
         <f>'LCOF WACC Corrected'!F16</f>
-        <v>7.4462348540395871</v>
+        <v>7.7427423081525282</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -4462,11 +4462,11 @@
       </c>
       <c r="E4" s="10">
         <f>E3/Inputs!$C$6</f>
-        <v>5.0866884642396721</v>
+        <v>5.2458622535886903</v>
       </c>
       <c r="F4" s="10">
         <f>F3/Inputs!$C$6</f>
-        <v>5.3048180251054236</v>
+        <v>5.4639918144544435</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>131</v>
@@ -4484,11 +4484,11 @@
       </c>
       <c r="L4" s="10">
         <f>L3/Inputs!$C$6</f>
-        <v>8.0554647214004547</v>
+        <v>8.3849174481926134</v>
       </c>
       <c r="M4" s="10">
         <f>M3/Inputs!$C$6</f>
-        <v>8.2735942822662079</v>
+        <v>8.6030470090583648</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -4500,19 +4500,19 @@
       </c>
       <c r="C5" s="13">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="D5" s="13">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="E5" s="13">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="F5" s="13">
         <f>Inputs!$C$18</f>
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>132</v>
@@ -4730,19 +4730,19 @@
       </c>
       <c r="C10" s="10">
         <f>(C4-C5) / C9 * 10^6</f>
-        <v>1053.0156898248665</v>
+        <v>731.59176104352218</v>
       </c>
       <c r="D10" s="10">
         <f>(D4-D5) / D9 * 10^6</f>
-        <v>1131.3935221529064</v>
+        <v>809.96959337156193</v>
       </c>
       <c r="E10" s="10">
         <f>(E4-E5) / E9 * 10^6</f>
-        <v>1530.9380529306461</v>
+        <v>1266.3610849621634</v>
       </c>
       <c r="F10" s="10">
         <f>(F4-F5) / F9 * 10^6</f>
-        <v>1608.8403423048896</v>
+        <v>1344.2633743364079</v>
       </c>
       <c r="H10" s="16" t="s">
         <v>138</v>
@@ -4760,11 +4760,11 @@
       </c>
       <c r="L10" s="10">
         <f>(L4-L5) / L9 * 10^6</f>
-        <v>2591.1999732077488</v>
+        <v>2708.8599618669296</v>
       </c>
       <c r="M10" s="10">
         <f>(M4-M5) / M9 * 10^6</f>
-        <v>2669.1022625819933</v>
+        <v>2786.7622512411726</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="C15" s="22">
         <f>C14*Inputs!$C$33 * 10^-6</f>
-        <v>0.132924996864</v>
+        <v>0.14483286116639998</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>141</v>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="J15" s="22">
         <f>J14*Inputs!$C$32 * 10^-6</f>
-        <v>0.35502051245760002</v>
+        <v>0.37966702229279997</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C16" s="22">
         <f>F4+C15</f>
-        <v>5.4377430219694238</v>
+        <v>5.6088246756208431</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>142</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="J16" s="22">
         <f>M4+J15</f>
-        <v>8.6286147947238074</v>
+        <v>8.9827140313511649</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C17" s="5">
         <f>(C16-C5) /C9 * 10^6</f>
-        <v>1656.3128697774173</v>
+        <v>1395.9886490616823</v>
       </c>
       <c r="H17" s="21" t="s">
         <v>143</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="J17" s="5">
         <f>(J16-J5) /J9 * 10^6</f>
-        <v>2795.8934713732015</v>
+        <v>2922.3556578345792</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity/Harmonization_SAF/Harmonization Sheets/Gray_2024_Harmonization.xlsx
+++ b/Sensitivity/Harmonization_SAF/Harmonization Sheets/Gray_2024_Harmonization.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{D6FDD79B-056F-1B49-B921-33F727076B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A10E616-15C1-4160-B161-F1384B01E0DE}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -854,7 +854,7 @@
         </row>
         <row r="34">
           <cell r="C34">
-            <v>523</v>
+            <v>497</v>
           </cell>
         </row>
       </sheetData>
@@ -1202,11 +1202,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="24.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C33" s="5">
         <f>[1]Inputs!C34</f>
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
@@ -1587,7 +1587,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="49" bestFit="1" customWidth="1"/>
   </cols>
@@ -2194,7 +2194,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
   </cols>
@@ -2532,9 +2532,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="30.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2831,13 +2831,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.09765625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3179,7 +3179,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
@@ -3523,7 +3523,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="B7" s="17">
         <f>Inputs!C33 * Inputs!C6</f>
-        <v>470.7</v>
+        <v>447.3</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>74</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="B8" s="13">
         <f>B7*B6*10^3 / 10^6</f>
-        <v>67.942720800000004</v>
+        <v>64.565071199999991</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>80</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B14" s="13">
         <f>(B4+B8+B11)  * 10^6/ B12</f>
-        <v>494.49509966618257</v>
+        <v>485.42271288133156</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>71</v>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="B15" s="13">
         <f>B14*'Study Parameters'!$C$28/10^3</f>
-        <v>5.8795467350309112</v>
+        <v>5.7716760561590323</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>120</v>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="B16" s="10">
         <f>B15 * Inputs!$C$15</f>
-        <v>4.7212760282298216</v>
+        <v>4.6346558730957028</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>121</v>
@@ -3867,7 +3867,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="M2" s="5">
         <f>B8</f>
-        <v>67.942720800000004</v>
+        <v>64.565071199999991</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="B7" s="17">
         <f>Inputs!C33 * Inputs!C6</f>
-        <v>470.7</v>
+        <v>447.3</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>74</v>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="B8" s="13">
         <f>B7*B6*10^3 / 10^6</f>
-        <v>67.942720800000004</v>
+        <v>64.565071199999991</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>80</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="M8" s="20">
         <f>M2/SUM($M$2:$M$5)</f>
-        <v>0.40056503743767941</v>
+        <v>0.38838573814098071</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="M9" s="20">
         <f t="shared" ref="M9:M11" si="1">M3/SUM($M$2:$M$5)</f>
-        <v>0.33982874012219116</v>
+        <v>0.34673336897112639</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="M10" s="20">
         <f t="shared" si="1"/>
-        <v>0.17706742419807384</v>
+        <v>0.18066507413458324</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="M11" s="20">
         <f t="shared" si="1"/>
-        <v>8.2538798242055553E-2</v>
+        <v>8.4215818753309621E-2</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="B14" s="13">
         <f>(B4+B8+B11)  * 10^6/ B12</f>
-        <v>515.05682883981103</v>
+        <v>505.98444205496003</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>71</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="B15" s="13">
         <f>B14*'Study Parameters'!$C$28/10^3</f>
-        <v>6.1240256949053533</v>
+        <v>6.0161550160334745</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>120</v>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="B16" s="10">
         <f>B15 * Inputs!$C$15</f>
-        <v>4.917592633008999</v>
+        <v>4.8309724778748802</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>121</v>
@@ -4335,12 +4335,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="14.75" customWidth="1"/>
-    <col min="6" max="6" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.75" customWidth="1"/>
-    <col min="13" max="13" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.69921875" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.69921875" customWidth="1"/>
+    <col min="13" max="13" width="13.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -4416,11 +4416,11 @@
       </c>
       <c r="E3" s="10">
         <f>'LCOF DAC Corrected'!B16</f>
-        <v>4.7212760282298216</v>
+        <v>4.6346558730957028</v>
       </c>
       <c r="F3" s="10">
         <f>'LCOF WACC Corrected'!B16</f>
-        <v>4.917592633008999</v>
+        <v>4.8309724778748802</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>131</v>
@@ -4462,11 +4462,11 @@
       </c>
       <c r="E4" s="10">
         <f>E3/Inputs!$C$6</f>
-        <v>5.2458622535886903</v>
+        <v>5.1496176367730033</v>
       </c>
       <c r="F4" s="10">
         <f>F3/Inputs!$C$6</f>
-        <v>5.4639918144544435</v>
+        <v>5.3677471976387556</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>131</v>
@@ -4738,11 +4738,11 @@
       </c>
       <c r="E10" s="10">
         <f>(E4-E5) / E9 * 10^6</f>
-        <v>1266.3610849621634</v>
+        <v>1231.9885040055492</v>
       </c>
       <c r="F10" s="10">
         <f>(F4-F5) / F9 * 10^6</f>
-        <v>1344.2633743364079</v>
+        <v>1309.8907933797927</v>
       </c>
       <c r="H10" s="16" t="s">
         <v>138</v>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="C15" s="22">
         <f>C14*Inputs!$C$33 * 10^-6</f>
-        <v>0.14483286116639998</v>
+        <v>0.1376327571696</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>141</v>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C16" s="22">
         <f>F4+C15</f>
-        <v>5.6088246756208431</v>
+        <v>5.5053799548083555</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>142</v>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C17" s="5">
         <f>(C16-C5) /C9 * 10^6</f>
-        <v>1395.9886490616823</v>
+        <v>1359.0446395336389</v>
       </c>
       <c r="H17" s="21" t="s">
         <v>143</v>
